--- a/ECMAC.xlsx
+++ b/ECMAC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="89">
   <si>
     <t/>
   </si>
@@ -58,21 +58,30 @@
     <t>PT,(E-3B)</t>
   </si>
   <si>
+    <t>20142567</t>
+  </si>
+  <si>
+    <t>SUTRA KONDOM RAPET3S</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>20134971</t>
   </si>
   <si>
     <t>SUTRA KONDOM 003 2'S</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>20032984</t>
   </si>
   <si>
     <t>DUREX PLY.LBE FEEL50</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
@@ -82,7 +91,7 @@
     <t>VIGEL LUBRICATING 60</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>PT,(E-4B)</t>
@@ -94,7 +103,7 @@
     <t>DUREX LUBESTRBRY50ML</t>
   </si>
   <si>
-    <t>7</t>
+    <t>8</t>
   </si>
   <si>
     <t>20131512</t>
@@ -103,7 +112,7 @@
     <t>SUTRA LUBRCNT GEL 50</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
@@ -115,7 +124,7 @@
     <t>TESTPACK ALAT TES</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>10007241</t>
@@ -124,7 +133,7 @@
     <t>SENSITIF STRIP</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t>10013365</t>
@@ -133,7 +142,7 @@
     <t>AKURAT STRIP PCS</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>20141773</t>
@@ -142,7 +151,7 @@
     <t>SUTRA KONDOM CINTA3S</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>20088105</t>
@@ -239,9 +248,6 @@
   </si>
   <si>
     <t>IM3 KARTU PERDANA</t>
-  </si>
-  <si>
-    <t>13</t>
   </si>
   <si>
     <t>20131412</t>
@@ -664,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -772,7 +778,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -792,16 +798,16 @@
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
@@ -809,30 +815,30 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -852,27 +858,27 @@
         <v>30</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -892,7 +898,7 @@
         <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -912,7 +918,7 @@
         <v>40</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -932,7 +938,7 @@
         <v>43</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -946,13 +952,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -966,233 +972,233 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1206,33 +1212,33 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1246,13 +1252,13 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1266,33 +1272,33 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1306,13 +1312,33 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>20</v>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/ECMAC.xlsx
+++ b/ECMAC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="89">
   <si>
     <t/>
   </si>
@@ -670,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -678,10 +678,11 @@
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -700,8 +701,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -717,11 +724,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -737,11 +744,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -757,11 +764,11 @@
       <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -777,11 +784,11 @@
       <c r="E5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
@@ -797,11 +804,11 @@
       <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -817,11 +824,11 @@
       <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
@@ -837,11 +844,11 @@
       <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>28</v>
       </c>
@@ -857,11 +864,11 @@
       <c r="E9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>31</v>
       </c>
@@ -877,11 +884,11 @@
       <c r="E10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
@@ -897,11 +904,11 @@
       <c r="E11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>38</v>
       </c>
@@ -917,11 +924,11 @@
       <c r="E12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>41</v>
       </c>
@@ -937,11 +944,11 @@
       <c r="E13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>44</v>
       </c>
@@ -957,11 +964,11 @@
       <c r="E14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>47</v>
       </c>
@@ -977,11 +984,11 @@
       <c r="E15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -997,11 +1004,11 @@
       <c r="E16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>52</v>
       </c>
@@ -1017,11 +1024,11 @@
       <c r="E17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>54</v>
       </c>
@@ -1037,11 +1044,11 @@
       <c r="E18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>56</v>
       </c>
@@ -1057,11 +1064,11 @@
       <c r="E19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
@@ -1077,11 +1084,11 @@
       <c r="E20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>60</v>
       </c>
@@ -1097,11 +1104,11 @@
       <c r="E21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>62</v>
       </c>
@@ -1117,11 +1124,11 @@
       <c r="E22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>64</v>
       </c>
@@ -1137,11 +1144,11 @@
       <c r="E23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>66</v>
       </c>
@@ -1157,11 +1164,11 @@
       <c r="E24" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>68</v>
       </c>
@@ -1177,11 +1184,11 @@
       <c r="E25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>70</v>
       </c>
@@ -1197,11 +1204,11 @@
       <c r="E26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -1217,11 +1224,11 @@
       <c r="E27" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>75</v>
       </c>
@@ -1237,11 +1244,11 @@
       <c r="E28" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>77</v>
       </c>
@@ -1257,11 +1264,11 @@
       <c r="E29" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>79</v>
       </c>
@@ -1277,11 +1284,11 @@
       <c r="E30" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>81</v>
       </c>
@@ -1297,11 +1304,11 @@
       <c r="E31" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
@@ -1317,11 +1324,11 @@
       <c r="E32" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>87</v>
       </c>
@@ -1337,7 +1344,7 @@
       <c r="E33" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/ECMAC.xlsx
+++ b/ECMAC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
   <si>
     <t/>
   </si>
@@ -130,19 +130,13 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20019566</t>
-  </si>
-  <si>
-    <t>IM3 KARTU PERDANA</t>
+    <t>20124879</t>
+  </si>
+  <si>
+    <t>NTFLX GIFT CARD 160K</t>
   </si>
   <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>20124879</t>
-  </si>
-  <si>
-    <t>NTFLX GIFT CARD 160K</t>
   </si>
   <si>
     <t>20133887</t>
@@ -568,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -876,7 +870,7 @@
         <v>41</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -896,7 +890,7 @@
         <v>41</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -913,18 +907,18 @@
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -933,49 +927,29 @@
         <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="1" t="s">
         <v>38</v>
       </c>
     </row>
